--- a/discrate/studies.xlsx
+++ b/discrate/studies.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Havrankova\Dropbox\36_Discount_Rate\REVISION\WEB\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4A0685CE-B37A-40AF-B8B0-92823CCC1B77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{03B969B1-C122-4866-918E-F4BE6F560876}"/>
@@ -1428,6 +1423,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>